--- a/branches/dev/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:08:36+00:00</t>
+    <t>2026-09-14T20:46:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/branches/dev/CodeSystem-mii-cs-consent-version-modules.xlsx
+++ b/branches/dev/CodeSystem-mii-cs-consent-version-modules.xlsx
@@ -67,7 +67,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T20:46:54+00:00</t>
+    <t>2026-10-06T12:38:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
